--- a/data/upcoming.xlsx
+++ b/data/upcoming.xlsx
@@ -49,10 +49,10 @@
     <t>Seminar</t>
   </si>
   <si>
-    <t xml:space="preserve"> https://forms.gle/SEmmrAe1qzwLsh1y8</t>
+    <t>Zooming in on Feasibility and Data Quality Assessments - Part 2</t>
   </si>
   <si>
-    <t>Zooming in on Feasibility and Data Quality Assessments</t>
+    <t>https://forms.cloud.microsoft/e/TYpbQDMkLF</t>
   </si>
 </sst>
 </file>
@@ -181,7 +181,7 @@
         <xdr:cNvPr id="2" name="image1.gif" descr="https://ssl.gstatic.com/ui/v1/icons/mail/images/cleardot.gif">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -215,7 +215,7 @@
         <xdr:cNvPr id="3" name="image1.gif" descr="https://ssl.gstatic.com/ui/v1/icons/mail/images/cleardot.gif">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -532,17 +532,17 @@
     </row>
     <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="str">
-        <f>"16.09.2026"</f>
-        <v>16.09.2026</v>
+        <f>"25.11.2026"</f>
+        <v>25.11.2026</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5242,7 +5242,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://forms.gle/y96E9KkUNqYgKbJv7"/>
+    <hyperlink ref="D2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
